--- a/Doc/ConfigPrj/ExcelCfg/STM32G474RE/STM32G474RE_HwCfg.xlsx
+++ b/Doc/ConfigPrj/ExcelCfg/STM32G474RE/STM32G474RE_HwCfg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\Gamma_fCreateCfg\Doc\ConfigPrj\ExcelCfg\STM32G474RE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\fIntegration_H7\Doc\ConfigPrj\ExcelCfg\STM32G474RE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067BA571-2B01-4CF8-A8D9-FA6606A17F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084539DC-6F2D-4FE7-8834-12505453EB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
   </bookViews>
   <sheets>
     <sheet name="General_Info" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="500">
   <si>
     <t>Colonne1</t>
   </si>
@@ -62,9 +62,6 @@
     <t>TIMER_1</t>
   </si>
   <si>
-    <t>TIMER_3</t>
-  </si>
-  <si>
     <t>TIMER_15</t>
   </si>
   <si>
@@ -800,9 +797,6 @@
     <t>HRTIM1</t>
   </si>
   <si>
-    <t>TIMER_2</t>
-  </si>
-  <si>
     <t>TIMER_4</t>
   </si>
   <si>
@@ -1530,6 +1524,27 @@
   </si>
   <si>
     <t>GPIO_AF11_FDCAN3</t>
+  </si>
+  <si>
+    <t>TI1_Port</t>
+  </si>
+  <si>
+    <t>TI1_Pin</t>
+  </si>
+  <si>
+    <t>TI2_Port</t>
+  </si>
+  <si>
+    <t>TI2_Pin</t>
+  </si>
+  <si>
+    <t>Timer</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Alternate Function</t>
   </si>
 </sst>
 </file>
@@ -1676,7 +1691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1697,11 +1712,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -1829,6 +1845,194 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border outline="0">
@@ -4374,6 +4578,22 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{256E63F7-EF05-4679-832E-05A9EE093878}" name="FMKIO_EcdrCfg" displayName="FMKIO_EcdrCfg" ref="A34:G35" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+  <autoFilter ref="A34:G35" xr:uid="{256E63F7-EF05-4679-832E-05A9EE093878}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{74AA91EE-00D8-40CF-9F42-67EACE0D9C4C}" name="TI1_Port" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{3DD77F7D-1104-4312-8394-A1A72AB72CC2}" name="TI1_Pin" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{8E67D3FE-CFCF-4F6B-AF08-A5775354CB1F}" name="TI2_Port" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{DA2408AA-9077-43A1-9C98-C1CE03F9EB79}" name="TI2_Pin" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E995C9CD-1E23-4255-B933-582EF7B591FB}" name="Timer" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{44E17610-C7FD-45EC-B7AE-2FD41A3055B9}" name="Channel" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{782E3FB9-8180-45F3-A753-B1408125736E}" name="Alternate Function" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{684AB3A4-4693-477C-AADC-64EBB335C3E9}" name="FMKTIM_EvntTimer" displayName="FMKTIM_EvntTimer" ref="B4:C6" totalsRowShown="0">
   <autoFilter ref="B4:C6" xr:uid="{684AB3A4-4693-477C-AADC-64EBB335C3E9}"/>
   <tableColumns count="2">
@@ -4384,7 +4604,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{CCB68487-82CB-434C-A0E4-701B1FDDACF5}" name="FMKTIM_IRQNHandler" displayName="FMKTIM_IRQNHandler" ref="F4:G17" totalsRowShown="0">
   <autoFilter ref="F4:G17" xr:uid="{CCB68487-82CB-434C-A0E4-701B1FDDACF5}"/>
   <tableColumns count="2">
@@ -4395,7 +4615,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{953E7E02-522E-4F1F-B136-4D0BF069F045}" name="FMKHRT_IrqHandler" displayName="FMKHRT_IrqHandler" ref="Y5:Y12" totalsRowShown="0">
   <autoFilter ref="Y5:Y12" xr:uid="{953E7E02-522E-4F1F-B136-4D0BF069F045}"/>
   <tableColumns count="1">
@@ -4405,7 +4625,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{A4F27ADC-56A6-479B-93EF-D6AA72368D72}" name="FMKCDA_CalibrationOthers" displayName="FMKCDA_CalibrationOthers" ref="I3:M6" totalsRowShown="0">
   <autoFilter ref="I3:M6" xr:uid="{A4F27ADC-56A6-479B-93EF-D6AA72368D72}"/>
   <tableColumns count="5">
@@ -4414,19 +4634,6 @@
     <tableColumn id="3" xr3:uid="{0793AAF2-321B-4695-AEBB-122FAB9D49F7}" name="Adc Vref"/>
     <tableColumn id="4" xr3:uid="{F1198D75-5BAD-4CA5-814F-DDA2BB66E5F2}" name="Channel Vref"/>
     <tableColumn id="5" xr3:uid="{6C202CA4-44FC-4E46-A4B5-AF7389AC3A4D}" name="Enable"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{99B4503A-67B2-48AD-BE25-2B3425F892A9}" name="FMKCDA_VoltageRef" displayName="FMKCDA_VoltageRef" ref="T17:W22" totalsRowShown="0">
-  <autoFilter ref="T17:W22" xr:uid="{99B4503A-67B2-48AD-BE25-2B3425F892A9}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0BCC2BC4-7FF0-4C14-809D-9D95A3225151}" name="Vref Calib"/>
-    <tableColumn id="2" xr3:uid="{0E78A6D4-DF9E-4966-A80E-64FE5BD9F1E2}" name="address  hexacecimal"/>
-    <tableColumn id="4" xr3:uid="{4C711A0D-EAF5-4229-B4D2-99254AE9F9BA}" name="Adc Vref"/>
-    <tableColumn id="5" xr3:uid="{0B4759AE-B188-4822-92BB-EEEB3203C895}" name="Channel Vref"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4444,6 +4651,19 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{99B4503A-67B2-48AD-BE25-2B3425F892A9}" name="FMKCDA_VoltageRef" displayName="FMKCDA_VoltageRef" ref="T17:W22" totalsRowShown="0">
+  <autoFilter ref="T17:W22" xr:uid="{99B4503A-67B2-48AD-BE25-2B3425F892A9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0BCC2BC4-7FF0-4C14-809D-9D95A3225151}" name="Vref Calib"/>
+    <tableColumn id="2" xr3:uid="{0E78A6D4-DF9E-4966-A80E-64FE5BD9F1E2}" name="address  hexacecimal"/>
+    <tableColumn id="4" xr3:uid="{4C711A0D-EAF5-4229-B4D2-99254AE9F9BA}" name="Adc Vref"/>
+    <tableColumn id="5" xr3:uid="{0B4759AE-B188-4822-92BB-EEEB3203C895}" name="Channel Vref"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{FAF38277-E25D-413A-A145-AFBC74566FF1}" name="FMKCDA_IRQNHandler" displayName="FMKCDA_IRQNHandler" ref="E8:F12" totalsRowShown="0">
   <autoFilter ref="E8:F12" xr:uid="{FAF38277-E25D-413A-A145-AFBC74566FF1}"/>
   <tableColumns count="2">
@@ -4454,7 +4674,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}" name="FMKMAC_Cfg" displayName="FMKMAC_Cfg" ref="B2:E16" totalsRowShown="0">
   <autoFilter ref="B2:E16" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}"/>
   <tableColumns count="4">
@@ -4467,7 +4687,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}" name="FMKMAC_IRQN" displayName="FMKMAC_IRQN" ref="J3:K18" totalsRowShown="0">
   <autoFilter ref="J3:K18" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}"/>
   <tableColumns count="2">
@@ -4478,7 +4698,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{9E75F4B3-8C66-44CB-A927-82E8A09563A2}" name="FMKMAC_DMAMUX" displayName="FMKMAC_DMAMUX" ref="P3:P4" totalsRowShown="0">
   <autoFilter ref="P3:P4" xr:uid="{9E75F4B3-8C66-44CB-A927-82E8A09563A2}"/>
   <tableColumns count="1">
@@ -4488,7 +4708,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{3568793B-2270-4B9A-A9E5-55F929444AFF}" name="fdcan_irqn_handler" displayName="fdcan_irqn_handler" ref="B5:B11" totalsRowShown="0">
   <autoFilter ref="B5:B11" xr:uid="{3568793B-2270-4B9A-A9E5-55F929444AFF}"/>
   <tableColumns count="1">
@@ -4498,7 +4718,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{313ACF3F-AE43-48C2-87A6-B02CD6ECDE78}" name="Fdcan_Info" displayName="Fdcan_Info" ref="D5:G8" totalsRowShown="0">
   <autoFilter ref="D5:G8" xr:uid="{313ACF3F-AE43-48C2-87A6-B02CD6ECDE78}"/>
   <tableColumns count="4">
@@ -4511,7 +4731,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{CF6032E9-4D15-4575-AD94-133BB9C2FD31}" name="FMKSRL_INFO" displayName="FMKSRL_INFO" ref="E2:M7" totalsRowShown="0">
   <autoFilter ref="E2:M7" xr:uid="{CF6032E9-4D15-4575-AD94-133BB9C2FD31}"/>
   <tableColumns count="9">
@@ -4529,7 +4749,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table38.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{234B95CE-5663-49A6-97EA-930C7F4E968E}" name="Tableau21" displayName="Tableau21" ref="E20:G28" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="E20:G28" xr:uid="{234B95CE-5663-49A6-97EA-930C7F4E968E}"/>
   <tableColumns count="3">
@@ -4555,6 +4775,9 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{9B4F1398-0B6D-4B55-A4C3-611E0B66A012}" name="GI_RCC_CLOCK" displayName="GI_RCC_CLOCK" ref="D18:F75" totalsRowShown="0">
   <autoFilter ref="D18:F75" xr:uid="{9B4F1398-0B6D-4B55-A4C3-611E0B66A012}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D19:F75">
+    <sortCondition ref="D18:D75"/>
+  </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{402A3AD5-0AFA-40A5-A5A4-0D9CB2EED72D}" name="RCC_ClockName"/>
     <tableColumn id="2" xr3:uid="{05025EF0-98DC-4B06-8DD6-ABD9D73D50B7}" name="Clock Soure"/>
@@ -4955,33 +5178,33 @@
   <sheetData>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="R17" t="s">
+        <v>453</v>
+      </c>
+      <c r="S17" t="s">
+        <v>454</v>
+      </c>
+      <c r="T17" t="s">
         <v>455</v>
-      </c>
-      <c r="S17" t="s">
-        <v>456</v>
-      </c>
-      <c r="T17" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F18" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
         <v>57</v>
-      </c>
-      <c r="I18" t="s">
-        <v>58</v>
       </c>
       <c r="K18" t="s">
         <v>2</v>
@@ -4990,16 +5213,16 @@
         <v>3</v>
       </c>
       <c r="M18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="O18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -5010,78 +5233,78 @@
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>236</v>
       </c>
       <c r="E19" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F19" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K19" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="L19">
         <v>4</v>
       </c>
       <c r="M19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O19" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E20" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K20" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="L20">
         <v>4</v>
       </c>
       <c r="M20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
@@ -5089,432 +5312,432 @@
         <v>233</v>
       </c>
       <c r="E21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K21" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AC21">
         <v>8</v>
       </c>
       <c r="AD21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K22" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="L22">
         <v>4</v>
       </c>
       <c r="M22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AC22">
         <v>8</v>
       </c>
       <c r="AD22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="F23" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K23" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="L23">
         <v>4</v>
       </c>
       <c r="M23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E24" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F24" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K24" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F25" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K25" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="L25">
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="O25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F26" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K26" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="L26">
         <v>4</v>
       </c>
       <c r="M26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" t="s">
         <v>279</v>
       </c>
-      <c r="B27" t="s">
-        <v>281</v>
-      </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F27" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K27" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="L27">
         <v>2</v>
       </c>
       <c r="M27" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B28">
         <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F28" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K28" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="L28">
         <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N28" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B29">
         <v>170</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F29" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K29" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="L29">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N29" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O29" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="E30" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F30" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K30" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="L30">
         <v>4</v>
       </c>
       <c r="M30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F31" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F32" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F33" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="s">
         <v>9</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="34" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E34" t="s">
         <v>302</v>
       </c>
       <c r="F34" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>16</v>
@@ -5522,22 +5745,22 @@
     </row>
     <row r="35" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F35" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q35">
         <v>16</v>
@@ -5545,80 +5768,80 @@
     </row>
     <row r="36" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F36" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q36">
         <v>16</v>
       </c>
       <c r="Y36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F37" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q37">
         <v>16</v>
       </c>
       <c r="Y37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F38" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q38">
         <v>16</v>
@@ -5626,22 +5849,22 @@
     </row>
     <row r="39" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E39" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F39" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q39">
         <v>16</v>
@@ -5649,1104 +5872,1104 @@
     </row>
     <row r="40" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="E40" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F40" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P40" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Q40">
         <v>11</v>
       </c>
       <c r="V40" t="s">
+        <v>16</v>
+      </c>
+      <c r="W40" t="s">
         <v>17</v>
       </c>
-      <c r="W40" t="s">
-        <v>18</v>
-      </c>
       <c r="X40" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Y40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Z40" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="E41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F41" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="V41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W41">
         <v>19</v>
       </c>
       <c r="X41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="E42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F42" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H42" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W42">
         <v>19</v>
       </c>
       <c r="X42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F43" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V43" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W43">
         <v>19</v>
       </c>
       <c r="X43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Y43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V44" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W44">
         <v>19</v>
       </c>
       <c r="X44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E45" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V45" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="W45">
         <v>19</v>
       </c>
       <c r="X45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>225</v>
+        <v>86</v>
       </c>
       <c r="E46" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F46" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF46" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="E47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F47" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF47" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="4:33" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="E48" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="F48" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF48" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F49" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF49" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>86</v>
+        <v>248</v>
       </c>
       <c r="E50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F50" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E51" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F51" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="E52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F52" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF52" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="E53" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F53" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF53" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="E54" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F54" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF54" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>277</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F55" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF55" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>278</v>
+        <v>70</v>
       </c>
       <c r="E56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F56" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF56" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>218</v>
+        <v>72</v>
       </c>
       <c r="E57" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F57" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H57" t="s">
+        <v>67</v>
+      </c>
+      <c r="I57" t="s">
         <v>68</v>
       </c>
-      <c r="I57" t="s">
-        <v>69</v>
-      </c>
       <c r="AF57" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>216</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F58" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H58" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF58" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="F59" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF59" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="E60" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F60" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF60" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E61" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F61" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H61" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF61" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="E62" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F62" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF62" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="E63" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F63" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="4:32" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>70</v>
+        <v>242</v>
       </c>
       <c r="E64" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F64" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F65" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>76</v>
+        <v>223</v>
       </c>
       <c r="E66" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F66" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E67" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F67" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="E68" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F68" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="E69" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F69" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H69" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>73</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F70" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H70" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E71" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F71" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E72" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F73" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="E74" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F74" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="E75" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F75" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I79" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="4:9" x14ac:dyDescent="0.3">
       <c r="H80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I81" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I89" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I91" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H95" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H96" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I96" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I97" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I98" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H99" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H100" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I101" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H102" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I102" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I103" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H104" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I104" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="105" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H105" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I105" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="106" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H106" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I106" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I107" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I108" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I109" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H110" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I110" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I111" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I112" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H113" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I113" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="114" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I114" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H115" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I115" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="116" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H117" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H118" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I118" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119" spans="8:9" x14ac:dyDescent="0.3">
       <c r="H119" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I119" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -6796,18 +7019,18 @@
   <sheetData>
     <row r="3" spans="2:15" ht="93.6" x14ac:dyDescent="1.75">
       <c r="B3" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="J5" t="s">
+        <v>443</v>
+      </c>
+      <c r="K5" t="s">
+        <v>444</v>
+      </c>
+      <c r="L5" t="s">
         <v>445</v>
-      </c>
-      <c r="K5" t="s">
-        <v>446</v>
-      </c>
-      <c r="L5" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
@@ -6863,18 +7086,18 @@
     </row>
     <row r="20" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E20" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>444</v>
-      </c>
       <c r="G20" s="10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E21" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F21" s="7">
         <f>$J$6 *$O$8 / $K$6</f>
@@ -6887,7 +7110,7 @@
     </row>
     <row r="22" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E22" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F22" s="8">
         <f>$J$6 *$O$9 / $K$6</f>
@@ -6900,7 +7123,7 @@
     </row>
     <row r="23" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E23" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F23" s="7">
         <f>$J$6 *$O$10 / $K$6</f>
@@ -6911,12 +7134,12 @@
         <v>16000</v>
       </c>
       <c r="R23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E24" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F24" s="8">
         <f>$J$6 *$O$11 / $K$6</f>
@@ -6929,7 +7152,7 @@
     </row>
     <row r="25" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E25" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F25" s="7">
         <f>$J$6 *$O$12 / $K$6</f>
@@ -6942,7 +7165,7 @@
     </row>
     <row r="26" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E26" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F26" s="8">
         <f>$J$6 *$O$13 / $K$6</f>
@@ -6955,7 +7178,7 @@
     </row>
     <row r="27" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E27" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F27" s="7">
         <f>$J$6 / $O$14 / $K$6</f>
@@ -6968,7 +7191,7 @@
     </row>
     <row r="28" spans="5:18" x14ac:dyDescent="0.3">
       <c r="E28" s="11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F28" s="11">
         <f>$J$6 / $O$15 / $K$6</f>
@@ -7024,875 +7247,903 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
+        <v>280</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" t="s">
+        <v>280</v>
+      </c>
+      <c r="V5" t="s">
         <v>54</v>
-      </c>
-      <c r="L5" t="s">
-        <v>282</v>
-      </c>
-      <c r="P5" t="s">
-        <v>56</v>
-      </c>
-      <c r="R5" t="s">
-        <v>282</v>
-      </c>
-      <c r="V5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
         <v>48</v>
       </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
       <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
         <v>23</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
       <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
         <v>42</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>43</v>
       </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
       <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" t="s">
-        <v>24</v>
-      </c>
       <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
         <v>42</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>43</v>
       </c>
-      <c r="T6" t="s">
-        <v>44</v>
-      </c>
       <c r="U6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="W6" t="s">
+        <v>22</v>
+      </c>
+      <c r="X6" t="s">
         <v>23</v>
       </c>
-      <c r="X6" t="s">
-        <v>24</v>
-      </c>
       <c r="Y6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>96</v>
-      </c>
-      <c r="J7" t="s">
-        <v>12</v>
-      </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="M7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="S7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="W7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AA7" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB7" t="s">
         <v>23</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>259</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>426</v>
+      </c>
+      <c r="M8" t="s">
+        <v>250</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" t="s">
+        <v>471</v>
+      </c>
+      <c r="S8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8" t="s">
+        <v>44</v>
+      </c>
+      <c r="U8" t="s">
+        <v>459</v>
+      </c>
+      <c r="W8" t="s">
+        <v>11</v>
+      </c>
+      <c r="X8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
-        <v>261</v>
-      </c>
-      <c r="H8" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="Y8" t="s">
         <v>428</v>
       </c>
-      <c r="M8" t="s">
-        <v>252</v>
-      </c>
-      <c r="N8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s">
-        <v>473</v>
-      </c>
-      <c r="S8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T8" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" t="s">
-        <v>461</v>
-      </c>
-      <c r="W8" t="s">
-        <v>12</v>
-      </c>
-      <c r="X8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>430</v>
-      </c>
       <c r="AA8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AB8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>105</v>
+      </c>
+      <c r="P9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s">
-        <v>106</v>
-      </c>
-      <c r="P9" t="s">
-        <v>13</v>
-      </c>
       <c r="Q9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="T9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>108</v>
+      </c>
+      <c r="P10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>109</v>
-      </c>
-      <c r="P10" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>41</v>
-      </c>
       <c r="R10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="S10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AA10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="S11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="T11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>259</v>
+      </c>
+      <c r="H12" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="Q12" t="s">
+        <v>26</v>
+      </c>
+      <c r="R12" t="s">
+        <v>468</v>
+      </c>
+      <c r="S12" t="s">
+        <v>254</v>
+      </c>
+      <c r="T12" t="s">
+        <v>44</v>
+      </c>
+      <c r="U12" t="s">
+        <v>460</v>
+      </c>
+      <c r="AA12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>261</v>
-      </c>
-      <c r="H12" t="s">
-        <v>97</v>
-      </c>
-      <c r="P12" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" t="s">
-        <v>470</v>
-      </c>
-      <c r="S12" t="s">
-        <v>256</v>
-      </c>
-      <c r="T12" t="s">
-        <v>45</v>
-      </c>
-      <c r="U12" t="s">
-        <v>462</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>12</v>
-      </c>
       <c r="AB12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="S13" t="s">
         <v>4</v>
       </c>
       <c r="T13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AA13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AB13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="AA14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q14" s="7" t="s">
+      <c r="AB14" t="s">
         <v>33</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="S14" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P15" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="S15" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="T15" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U15" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AA15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="P16" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R16" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="S16" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>465</v>
-      </c>
       <c r="T16" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AA16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AB16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="P17" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U17" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="P18" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="P19" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R19" s="8" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U19" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="25" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>282</v>
+      </c>
+      <c r="B25" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" t="s">
         <v>284</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>285</v>
       </c>
-      <c r="C25" t="s">
-        <v>286</v>
-      </c>
-      <c r="D25" t="s">
-        <v>287</v>
-      </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>257</v>
+      </c>
+      <c r="D27" t="s">
         <v>40</v>
       </c>
-      <c r="C27" t="s">
-        <v>259</v>
-      </c>
-      <c r="D27" t="s">
-        <v>41</v>
-      </c>
       <c r="E27" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F27" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="W27" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="W28" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:53" x14ac:dyDescent="0.3">
       <c r="W29" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AW29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BA29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:53" x14ac:dyDescent="0.3">
       <c r="W30" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AW30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY30" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA30" t="s">
         <v>93</v>
-      </c>
-      <c r="BA30" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:53" x14ac:dyDescent="0.3">
       <c r="W31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AW31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BA31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:53" x14ac:dyDescent="0.3">
       <c r="W32" t="s">
+        <v>359</v>
+      </c>
+      <c r="AW32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AY32" t="s">
+        <v>45</v>
+      </c>
+      <c r="BA32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="W33" t="s">
+        <v>360</v>
+      </c>
+      <c r="AW33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY33" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="W34" t="s">
         <v>361</v>
       </c>
-      <c r="AW32" t="s">
-        <v>27</v>
-      </c>
-      <c r="AY32" t="s">
-        <v>46</v>
-      </c>
-      <c r="BA32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="W33" t="s">
+      <c r="AW34" t="s">
+        <v>28</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="W35" t="s">
         <v>362</v>
       </c>
-      <c r="AW33" t="s">
-        <v>28</v>
-      </c>
-      <c r="AY33" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="W34" t="s">
-        <v>363</v>
-      </c>
-      <c r="AW34" t="s">
+      <c r="AW35" t="s">
         <v>29</v>
       </c>
-      <c r="AY34" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA34" t="s">
+      <c r="BA35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="W35" t="s">
-        <v>364</v>
-      </c>
-      <c r="AW35" t="s">
+    <row r="36" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW36" t="s">
         <v>30</v>
       </c>
-      <c r="BA35" t="s">
+      <c r="BA36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW36" t="s">
+    <row r="37" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW37" t="s">
         <v>31</v>
       </c>
-      <c r="BA36" t="s">
+      <c r="BA37" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW37" t="s">
+    <row r="38" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW38" t="s">
         <v>32</v>
       </c>
-      <c r="BA37" t="s">
+      <c r="BA38" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW38" t="s">
+    <row r="39" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW39" t="s">
         <v>33</v>
       </c>
-      <c r="BA38" t="s">
+      <c r="BA39" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW39" t="s">
+    <row r="40" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW40" t="s">
         <v>34</v>
       </c>
-      <c r="BA39" t="s">
+      <c r="BA40" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW40" t="s">
+    <row r="41" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW41" t="s">
         <v>35</v>
       </c>
-      <c r="BA40" t="s">
+      <c r="BA41" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="41" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW41" t="s">
-        <v>36</v>
-      </c>
-      <c r="BA41" t="s">
+    <row r="42" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW42" t="s">
+        <v>37</v>
+      </c>
+      <c r="BA42" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW42" t="s">
+    <row r="43" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW43" t="s">
         <v>38</v>
       </c>
-      <c r="BA42" t="s">
+      <c r="BA43" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW43" t="s">
+    <row r="44" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW44" t="s">
         <v>39</v>
       </c>
-      <c r="BA43" t="s">
+      <c r="BA44" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW44" t="s">
+    <row r="45" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AW45" t="s">
         <v>40</v>
       </c>
-      <c r="BA44" t="s">
+      <c r="BA45" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="AW45" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA45" t="s">
+    <row r="46" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="BA46" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="BA46" t="s">
+    <row r="47" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="BA47" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="23:53" x14ac:dyDescent="0.3">
-      <c r="BA47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="23:53" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:53" x14ac:dyDescent="0.3">
       <c r="BA48" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="57" spans="36:36" x14ac:dyDescent="0.3">
       <c r="AJ57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -7916,7 +8167,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="11">
+  <tableParts count="12">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -7928,6 +8179,7 @@
     <tablePart r:id="rId10"/>
     <tablePart r:id="rId11"/>
     <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -7963,10 +8215,10 @@
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -7977,126 +8229,126 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G6" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G8" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F9" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G9" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G10" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F11" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G11" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G12" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G15" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="F16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G16" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G17" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -8124,37 +8376,37 @@
     </row>
     <row r="6" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y11" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -8185,207 +8437,207 @@
   <sheetData>
     <row r="2" spans="5:17" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I2" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="5:17" x14ac:dyDescent="0.3">
       <c r="I3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" t="s">
         <v>118</v>
       </c>
-      <c r="L3" t="s">
-        <v>119</v>
-      </c>
       <c r="M3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="5:17" x14ac:dyDescent="0.3">
       <c r="I4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J4" t="s">
+        <v>477</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M4" t="s">
         <v>479</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>111</v>
-      </c>
-      <c r="M4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="5" spans="5:17" x14ac:dyDescent="0.3">
       <c r="I5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="5:17" x14ac:dyDescent="0.3">
       <c r="I6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J6" t="s">
         <v>265</v>
       </c>
-      <c r="J6" t="s">
-        <v>267</v>
-      </c>
       <c r="K6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F9" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F10" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F11" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="U17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V17" t="s">
+        <v>117</v>
+      </c>
+      <c r="W17" t="s">
         <v>118</v>
-      </c>
-      <c r="W17" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="18" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T18" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="U18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T19" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="U19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T20" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="U20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W20" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T21" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="U21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="20:23" x14ac:dyDescent="0.3">
       <c r="T22" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="U22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="V22" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="W22" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -8432,320 +8684,320 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s">
         <v>332</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>333</v>
       </c>
-      <c r="D2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E2" t="s">
-        <v>335</v>
-      </c>
       <c r="J2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="P4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s">
+        <v>373</v>
+      </c>
+      <c r="K10" t="s">
         <v>339</v>
-      </c>
-      <c r="C10" t="s">
-        <v>330</v>
-      </c>
-      <c r="D10" t="s">
-        <v>340</v>
-      </c>
-      <c r="E10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" t="s">
-        <v>375</v>
-      </c>
-      <c r="K10" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K13" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J14" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C15" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J16" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J18" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -8769,40 +9021,40 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
+        <v>481</v>
+      </c>
+      <c r="E5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" t="s">
         <v>483</v>
       </c>
-      <c r="E5" t="s">
-        <v>489</v>
-      </c>
-      <c r="F5" t="s">
-        <v>485</v>
-      </c>
       <c r="G5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -8813,13 +9065,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -8830,13 +9082,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -8847,17 +9099,17 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -8889,39 +9141,39 @@
   <sheetData>
     <row r="2" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" t="s">
         <v>284</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>285</v>
       </c>
-      <c r="K2" t="s">
-        <v>286</v>
-      </c>
-      <c r="L2" t="s">
-        <v>287</v>
-      </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G3">
         <v>256</v>
@@ -8930,27 +9182,27 @@
         <v>256</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G4">
         <v>256</v>
@@ -8959,27 +9211,27 @@
         <v>1024</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -8988,27 +9240,27 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s">
+        <v>257</v>
+      </c>
+      <c r="L5" t="s">
         <v>30</v>
       </c>
-      <c r="K5" t="s">
-        <v>259</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
       <c r="M5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -9017,27 +9269,27 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s">
+        <v>257</v>
+      </c>
+      <c r="L6" t="s">
         <v>32</v>
       </c>
-      <c r="K6" t="s">
-        <v>259</v>
-      </c>
-      <c r="L6" t="s">
-        <v>33</v>
-      </c>
       <c r="M6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="5:13" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -9046,19 +9298,19 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>257</v>
+      </c>
+      <c r="L7" t="s">
         <v>34</v>
       </c>
-      <c r="K7" t="s">
-        <v>259</v>
-      </c>
-      <c r="L7" t="s">
-        <v>35</v>
-      </c>
       <c r="M7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -9085,7 +9337,7 @@
   <sheetData>
     <row r="1" spans="3:14" ht="93.6" x14ac:dyDescent="1.75">
       <c r="D1" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="3:14" x14ac:dyDescent="0.3">
@@ -9095,10 +9347,10 @@
     </row>
     <row r="4" spans="3:14" x14ac:dyDescent="0.3">
       <c r="L4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="3:14" x14ac:dyDescent="0.3">
@@ -9111,19 +9363,19 @@
     </row>
     <row r="7" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F7" t="s">
+        <v>303</v>
+      </c>
+      <c r="G7" t="s">
+        <v>304</v>
+      </c>
+      <c r="J7" t="s">
         <v>307</v>
-      </c>
-      <c r="F7" t="s">
-        <v>305</v>
-      </c>
-      <c r="G7" t="s">
-        <v>306</v>
-      </c>
-      <c r="J7" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.3">
@@ -9144,7 +9396,7 @@
         <v>1969.2307692307693</v>
       </c>
       <c r="M8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="3:14" x14ac:dyDescent="0.3">
@@ -9159,12 +9411,12 @@
         <v>39.99972500189061</v>
       </c>
       <c r="L12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="3:14" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L13" t="e">
         <f>L5+(L5/J15)*M9</f>
@@ -9189,15 +9441,15 @@
         <v>16000</v>
       </c>
       <c r="J16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="J17" t="s">
+        <v>310</v>
+      </c>
+      <c r="L17" t="s">
         <v>312</v>
-      </c>
-      <c r="L17" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -9232,10 +9484,10 @@
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
+        <v>318</v>
+      </c>
+      <c r="K28" t="s">
         <v>320</v>
-      </c>
-      <c r="K28" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
@@ -9247,39 +9499,39 @@
         <v>0.5</v>
       </c>
       <c r="M29" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F30" t="s">
         <v>319</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>304</v>
+      </c>
+      <c r="I30" t="s">
+        <v>323</v>
+      </c>
+      <c r="J30" t="s">
         <v>321</v>
       </c>
-      <c r="G30" t="s">
-        <v>306</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="K30" t="s">
+        <v>324</v>
+      </c>
+      <c r="L30" t="s">
         <v>325</v>
       </c>
-      <c r="J30" t="s">
-        <v>323</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="M30" t="s">
+        <v>322</v>
+      </c>
+      <c r="O30" t="s">
         <v>326</v>
-      </c>
-      <c r="L30" t="s">
-        <v>327</v>
-      </c>
-      <c r="M30" t="s">
-        <v>324</v>
-      </c>
-      <c r="O30" t="s">
-        <v>328</v>
       </c>
       <c r="P30" t="e">
         <f>2^#REF!</f>
